--- a/data/trans_orig/P20D2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P20D2_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si durante su último ingreso estuvo acompañado/a por una mujer en 2023</t>
+          <t>Población según si durante su último ingreso estuvo acompañado/a por una mujer en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,82 +730,82 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>2041</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1580</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3060</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>63,62%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>11,83%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>95,38%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>2041</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>616</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3061</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>63,62%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>19,21%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>95,42%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>2041</t>
-        </is>
-      </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>604</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5365</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,82%</t>
         </is>
       </c>
     </row>
@@ -848,7 +848,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4277</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,62 +878,62 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>1026</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>847</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>5566</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>6,19%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>26,42%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>1026</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>4562</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>6,19%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>33,6%</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>9080</t>
+          <t>7874</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>149</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>3208</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>88,02%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9224</t>
+          <t>9626</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15568</t>
+          <t>15803</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>55,68%</t>
+          <t>58,11%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,98%</t>
+          <t>95,4%</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>4225</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>61,41%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>4923</t>
+          <t>5478</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1256,12 +1256,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4776</t>
+          <t>4919</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11555</t>
+          <t>11718</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>33,1%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>78,86%</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4610</t>
+          <t>4211</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2895</t>
+          <t>2269</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1374,7 +1374,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5320</t>
+          <t>5729</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>35,8%</t>
+          <t>38,56%</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1767</t>
+          <t>2082</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -1427,7 +1427,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>30,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>991</t>
+          <t>950</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,43%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2089</t>
+          <t>2086</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9018</t>
+          <t>8348</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,06%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>56,18%</t>
         </is>
       </c>
     </row>
@@ -1642,12 +1642,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1102</t>
+          <t>1229</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7749</t>
+          <t>8246</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1657,12 +1657,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>53,86%</t>
+          <t>57,32%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1677,7 +1677,7 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1370</t>
+          <t>1292</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
@@ -1692,7 +1692,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>31,35%</t>
+          <t>29,56%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1712,12 +1712,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3702</t>
+          <t>3763</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11232</t>
+          <t>11517</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>19,74%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>59,88%</t>
+          <t>61,4%</t>
         </is>
       </c>
     </row>
@@ -1760,7 +1760,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>6781</t>
+          <t>5600</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>47,13%</t>
+          <t>38,92%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>2518</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7373</t>
+          <t>7322</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,3%</t>
+          <t>39,03%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5064</t>
+          <t>4783</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12300</t>
+          <t>12276</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>33,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2830</t>
+          <t>2532</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>64,72%</t>
+          <t>57,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5342</t>
+          <t>5400</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13424</t>
+          <t>13634</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>72,68%</t>
         </is>
       </c>
     </row>
@@ -2098,12 +2098,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>491</t>
+          <t>483</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6891</t>
+          <t>6779</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2113,12 +2113,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>47,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2133,12 +2133,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>976</t>
+          <t>940</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5722</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2148,12 +2148,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>10,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2168,12 +2168,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2624</t>
+          <t>1999</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>10383</t>
+          <t>9678</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2183,12 +2183,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>8,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>44,72%</t>
+          <t>41,69%</t>
         </is>
       </c>
     </row>
@@ -2211,12 +2211,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>527</t>
+          <t>551</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6550</t>
+          <t>6455</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2226,12 +2226,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2246,12 +2246,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>157</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3688</t>
+          <t>3870</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2261,12 +2261,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,46%</t>
+          <t>43,51%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2281,12 +2281,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1341</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>7975</t>
+          <t>8056</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2296,12 +2296,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,7%</t>
         </is>
       </c>
     </row>
@@ -2324,12 +2324,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5523</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12453</t>
+          <t>12357</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>86,95%</t>
+          <t>86,28%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2359,12 +2359,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2095</t>
+          <t>2249</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6894</t>
+          <t>6804</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2374,12 +2374,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>23,56%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>76,5%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2394,12 +2394,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9708</t>
+          <t>9392</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>18171</t>
+          <t>17878</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2409,12 +2409,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>40,45%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>77,01%</t>
         </is>
       </c>
     </row>
@@ -2554,12 +2554,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>184</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>6580</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2569,12 +2569,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>49,1%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2589,12 +2589,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4281</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9692</t>
+          <t>9356</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2604,12 +2604,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>69,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2624,12 +2624,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5858</t>
+          <t>5528</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>13679</t>
+          <t>14275</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2639,12 +2639,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>54,25%</t>
         </is>
       </c>
     </row>
@@ -2667,12 +2667,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>513</t>
+          <t>475</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5508</t>
+          <t>5712</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,12 +2682,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,0%</t>
+          <t>44,59%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2707,7 +2707,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3471</t>
+          <t>3627</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2737,12 +2737,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>961</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6906</t>
+          <t>6699</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2752,12 +2752,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>26,25%</t>
+          <t>25,46%</t>
         </is>
       </c>
     </row>
@@ -2780,12 +2780,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4369</t>
+          <t>4544</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10895</t>
+          <t>10914</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,12 +2795,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,11%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,06%</t>
+          <t>85,21%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2815,12 +2815,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3062</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8411</t>
+          <t>8433</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2830,12 +2830,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2850,12 +2850,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>9799</t>
+          <t>8861</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18333</t>
+          <t>18245</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,12 +2865,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>33,68%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,68%</t>
+          <t>69,34%</t>
         </is>
       </c>
     </row>
@@ -3010,12 +3010,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>119</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3025,12 +3025,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22,85%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3045,12 +3045,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>348</t>
+          <t>327</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4659</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3060,12 +3060,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,27%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3080,12 +3080,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>515</t>
+          <t>562</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5472</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,12 +3095,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>52,35%</t>
+          <t>48,16%</t>
         </is>
       </c>
     </row>
@@ -3123,97 +3123,97 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>3413</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>11,65%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>2,49%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>34,36%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1157</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>402</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>3345</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>11,07%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>77,15%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>3510</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>11,65%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>2,08%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>35,35%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1157</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>3268</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>11,07%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>32,0%</t>
         </is>
       </c>
     </row>
@@ -3236,12 +3236,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>402</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3251,12 +3251,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>77,15%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3271,12 +3271,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3768</t>
+          <t>3698</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9186</t>
+          <t>9019</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3286,12 +3286,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,94%</t>
+          <t>37,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>92,49%</t>
+          <t>90,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3306,12 +3306,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3561</t>
+          <t>3919</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9451</t>
+          <t>9437</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3321,12 +3321,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>37,5%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,42%</t>
+          <t>90,29%</t>
         </is>
       </c>
     </row>
@@ -3466,12 +3466,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>5276</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17288</t>
+          <t>17301</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3481,12 +3481,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>27,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3501,12 +3501,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17670</t>
+          <t>17605</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30289</t>
+          <t>30255</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3516,12 +3516,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>36,9%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3536,12 +3536,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>26577</t>
+          <t>26995</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>43901</t>
+          <t>45125</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3551,12 +3551,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,5%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>40,96%</t>
         </is>
       </c>
     </row>
@@ -3579,12 +3579,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>4039</t>
+          <t>3991</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14848</t>
+          <t>14629</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,49%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3614,12 +3614,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2316</t>
+          <t>2276</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8424</t>
+          <t>8755</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3629,12 +3629,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,59%</t>
+          <t>18,28%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3649,12 +3649,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7887</t>
+          <t>7645</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>20244</t>
+          <t>19515</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3664,12 +3664,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>17,71%</t>
         </is>
       </c>
     </row>
@@ -3692,12 +3692,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>36456</t>
+          <t>36577</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>50242</t>
+          <t>50411</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3707,12 +3707,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,73%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>80,67%</t>
+          <t>80,95%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13339</t>
+          <t>13623</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>25565</t>
+          <t>26106</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3742,12 +3742,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>53292</t>
+          <t>52533</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>72047</t>
+          <t>72037</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3777,12 +3777,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>48,38%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>65,4%</t>
+          <t>65,39%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P20D2_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P20D2_2023-Clase-trans_orig.xlsx
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>667</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3060</t>
+          <t>3404</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>63,62%</t>
+          <t>55,25%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>90,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>2041</t>
+          <t>2088</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>604</t>
+          <t>601</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>5222</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>32,82%</t>
+          <t>29,5%</t>
         </is>
       </c>
     </row>
@@ -838,7 +838,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -848,12 +848,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5483</t>
+          <t>4915</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -908,7 +908,7 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -918,12 +918,12 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>5566</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>6,19%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>33,6%</t>
+          <t>31,34%</t>
         </is>
       </c>
     </row>
@@ -951,27 +951,27 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>12331</t>
+          <t>12771</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7874</t>
+          <t>9010</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13357</t>
+          <t>13925</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>92,32%</t>
+          <t>91,71%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>64,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1167</t>
+          <t>1691</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>376</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>44,75%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>82,84%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>13498</t>
+          <t>14461</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>9626</t>
+          <t>10632</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>15803</t>
+          <t>16702</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>81,49%</t>
+          <t>81,68%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,4%</t>
+          <t>94,34%</t>
         </is>
       </c>
     </row>
@@ -1064,17 +1064,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>13357</t>
+          <t>13925</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13357</t>
+          <t>13925</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13357</t>
+          <t>13925</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1099,17 +1099,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>17704</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1034</t>
+          <t>1075</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1191,12 +1191,12 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>4225</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>15,03%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>61,41%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,27 +1216,27 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>7350</t>
+          <t>8650</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>5478</t>
+          <t>6041</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>92,13%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>8384</t>
+          <t>9725</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4919</t>
+          <t>5850</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11718</t>
+          <t>13666</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>55,52%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>33,1%</t>
+          <t>33,4%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,02%</t>
         </is>
       </c>
     </row>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1085</t>
+          <t>940</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1304,12 +1304,12 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4211</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -1319,7 +1319,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>61,2%</t>
+          <t>53,81%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>468</t>
+          <t>472</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -1339,12 +1339,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2269</t>
+          <t>2385</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1553</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -1374,12 +1374,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>5729</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>10,45%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -1389,7 +1389,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>28,63%</t>
         </is>
       </c>
     </row>
@@ -1407,27 +1407,27 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4761</t>
+          <t>5702</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>2082</t>
+          <t>2146</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>73,89%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>27,8%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>677</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>950</t>
+          <t>3708</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>37,84%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>4922</t>
+          <t>6379</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2086</t>
+          <t>3165</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>8348</t>
+          <t>10841</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>56,18%</t>
+          <t>61,89%</t>
         </is>
       </c>
     </row>
@@ -1520,17 +1520,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>7717</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1555,17 +1555,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>14859</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14859</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14859</t>
+          <t>17516</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1637,32 +1637,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>4133</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1229</t>
+          <t>1181</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8246</t>
+          <t>8846</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1672,27 +1672,27 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>3193</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1292</t>
+          <t>1275</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,86%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>7165</t>
+          <t>7565</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>3817</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>11517</t>
+          <t>12298</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>38,2%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>17,07%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>54,97%</t>
         </is>
       </c>
     </row>
@@ -1750,7 +1750,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1452</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5600</t>
+          <t>6182</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,92%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1785,7 +1785,7 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>626</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2518</t>
+          <t>2754</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,37%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,59%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2037</t>
+          <t>2061</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>7322</t>
+          <t>6618</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>9,21%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>29,58%</t>
         </is>
       </c>
     </row>
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>8963</t>
+          <t>12091</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>4783</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>12276</t>
+          <t>15868</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>68,47%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>43,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,7 +1898,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>653</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>2532</t>
+          <t>2863</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>13,58%</t>
+          <t>13,85%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>60,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>9557</t>
+          <t>12744</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>5400</t>
+          <t>7573</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>13634</t>
+          <t>17081</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>56,97%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>33,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>76,36%</t>
         </is>
       </c>
     </row>
@@ -1976,17 +1976,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14387</t>
+          <t>17659</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14387</t>
+          <t>17659</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>14387</t>
+          <t>17659</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2011,17 +2011,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>18759</t>
+          <t>22370</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>18759</t>
+          <t>22370</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>18759</t>
+          <t>22370</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2093,32 +2093,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2369</t>
+          <t>2196</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>483</t>
+          <t>459</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6779</t>
+          <t>6234</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>43,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2128,32 +2128,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3189</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>960</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5702</t>
+          <t>6294</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>34,73%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,11%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>5458</t>
+          <t>5386</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1999</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9678</t>
+          <t>9645</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>23,51%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>38,63%</t>
         </is>
       </c>
     </row>
@@ -2206,32 +2206,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2365</t>
+          <t>2427</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>551</t>
+          <t>466</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6455</t>
+          <t>5838</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>40,44%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2241,32 +2241,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>1359</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>474</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3870</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>43,51%</t>
+          <t>39,3%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>3723</t>
+          <t>4168</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>1558</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>8056</t>
+          <t>8524</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>16,04%</t>
+          <t>16,69%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,14%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>9588</t>
+          <t>9811</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>6228</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>12357</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>43,14%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>86,28%</t>
+          <t>88,22%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>4447</t>
+          <t>5604</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2249</t>
+          <t>3104</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6804</t>
+          <t>8303</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>78,82%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>14035</t>
+          <t>15415</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>9392</t>
+          <t>10506</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17878</t>
+          <t>19387</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>60,45%</t>
+          <t>61,74%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>40,45%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,64%</t>
         </is>
       </c>
     </row>
@@ -2432,17 +2432,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>14322</t>
+          <t>14435</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14322</t>
+          <t>14435</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>14322</t>
+          <t>14435</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,17 +2467,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>23216</t>
+          <t>24969</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23216</t>
+          <t>24969</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>23216</t>
+          <t>24969</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2549,32 +2549,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>3166</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>753</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>6580</t>
+          <t>7212</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>22,68%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,32 +2584,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>7541</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3946</t>
+          <t>4640</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9356</t>
+          <t>10875</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>50,39%</t>
+          <t>48,54%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>70,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>9092</t>
+          <t>10707</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>5528</t>
+          <t>6836</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>14275</t>
+          <t>15917</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>53,96%</t>
         </is>
       </c>
     </row>
@@ -2662,32 +2662,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2203</t>
+          <t>2193</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>475</t>
+          <t>489</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>5712</t>
+          <t>5687</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>40,74%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1065</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
@@ -2707,12 +2707,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>3627</t>
+          <t>3748</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
@@ -2722,7 +2722,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>24,13%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,32 +2732,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>3267</t>
+          <t>3265</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>867</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>6699</t>
+          <t>6660</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>22,58%</t>
         </is>
       </c>
     </row>
@@ -2775,32 +2775,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>8319</t>
+          <t>8601</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4544</t>
+          <t>4548</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10914</t>
+          <t>11797</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>61,61%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>32,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,32 +2810,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>5634</t>
+          <t>6922</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3062</t>
+          <t>4073</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8433</t>
+          <t>10130</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>41,72%</t>
+          <t>44,56%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>22,68%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>62,45%</t>
+          <t>65,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>13952</t>
+          <t>15524</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8861</t>
+          <t>10503</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18245</t>
+          <t>19914</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>33,68%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,34%</t>
+          <t>67,52%</t>
         </is>
       </c>
     </row>
@@ -2888,17 +2888,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>13960</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>13960</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>13960</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,17 +2923,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>15535</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>15535</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>15535</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>26312</t>
+          <t>29495</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>26312</t>
+          <t>29495</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>26312</t>
+          <t>29495</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2990,7 +2990,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -3005,7 +3005,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>507</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
@@ -3040,32 +3040,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>2048</t>
+          <t>2220</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>350</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>46,27%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>2569</t>
+          <t>2727</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>562</t>
+          <t>492</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t>5549</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>24,58%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>49,04%</t>
         </is>
       </c>
     </row>
@@ -3153,32 +3153,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>248</t>
+          <t>233</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3413</t>
+          <t>3676</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,5%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,36%</t>
+          <t>34,01%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,7 +3188,7 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>1157</t>
+          <t>1243</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
@@ -3198,12 +3198,12 @@
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3345</t>
+          <t>3513</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,04%</t>
         </is>
       </c>
     </row>
@@ -3266,32 +3266,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>7346</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3698</t>
+          <t>4342</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>9019</t>
+          <t>9956</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>90,82%</t>
+          <t>92,11%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>7346</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>3919</t>
+          <t>4061</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>9437</t>
+          <t>10240</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>35,89%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,49%</t>
         </is>
       </c>
     </row>
@@ -3344,17 +3344,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>507</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>507</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>507</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3379,17 +3379,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>11316</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>11316</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>11316</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3461,32 +3461,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>10184</t>
+          <t>11077</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>5276</t>
+          <t>5818</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>17301</t>
+          <t>18504</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>27,78%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3496,32 +3496,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>24525</t>
+          <t>27121</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>17605</t>
+          <t>20871</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>30255</t>
+          <t>34136</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>36,77%</t>
+          <t>37,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>34709</t>
+          <t>38198</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>26995</t>
+          <t>28037</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>45125</t>
+          <t>47844</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>31,51%</t>
+          <t>30,96%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>24,5%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>38,78%</t>
         </is>
       </c>
     </row>
@@ -3574,32 +3574,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>8130</t>
+          <t>8149</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3991</t>
+          <t>3787</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>14629</t>
+          <t>14553</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>13,06%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3609,32 +3609,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>4633</t>
+          <t>5154</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2276</t>
+          <t>2544</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>8755</t>
+          <t>8839</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>16,02%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>12764</t>
+          <t>13303</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>7645</t>
+          <t>8133</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>19515</t>
+          <t>21281</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,25%</t>
         </is>
       </c>
     </row>
@@ -3687,32 +3687,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>43963</t>
+          <t>48976</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>36577</t>
+          <t>41618</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>50411</t>
+          <t>56405</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>58,73%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>80,95%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3722,32 +3722,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>18728</t>
+          <t>22893</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>13623</t>
+          <t>16459</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>26106</t>
+          <t>30027</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>41,5%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>29,83%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>62689</t>
+          <t>71869</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>52533</t>
+          <t>61038</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>72037</t>
+          <t>82148</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>58,25%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>47,69%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>65,39%</t>
+          <t>66,59%</t>
         </is>
       </c>
     </row>
@@ -3800,17 +3800,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3835,17 +3835,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>47886</t>
+          <t>55168</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>47886</t>
+          <t>55168</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>47886</t>
+          <t>55168</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>110162</t>
+          <t>123370</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>110162</t>
+          <t>123370</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>110162</t>
+          <t>123370</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
